--- a/TEST AUTOMATION PROJECT - CURA Healthcare Services/Documentation/Cura Healthcare Service - Test Scenarios - 01.xlsx
+++ b/TEST AUTOMATION PROJECT - CURA Healthcare Services/Documentation/Cura Healthcare Service - Test Scenarios - 01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mabai\Desktop\Testing 2.0\TEST AUTOMATION PROJECT - CURA Healthcare Services\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC1DE713-2B44-4C42-95F0-34BA3F11A3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2639B8-F8FD-4306-8224-5D3925B8547A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{38E3547D-513B-432E-9109-DF06D717D2E9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{38E3547D-513B-432E-9109-DF06D717D2E9}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -796,6 +796,9 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -806,6 +809,9 @@
       </c>
       <c r="C3" t="s">
         <v>26</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">

--- a/TEST AUTOMATION PROJECT - CURA Healthcare Services/Documentation/Cura Healthcare Service - Test Scenarios - 01.xlsx
+++ b/TEST AUTOMATION PROJECT - CURA Healthcare Services/Documentation/Cura Healthcare Service - Test Scenarios - 01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mabai\Desktop\Testing 2.0\TEST AUTOMATION PROJECT - CURA Healthcare Services\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2639B8-F8FD-4306-8224-5D3925B8547A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40185863-2D6D-490A-A55B-5DB61A21BF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{38E3547D-513B-432E-9109-DF06D717D2E9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{38E3547D-513B-432E-9109-DF06D717D2E9}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>

--- a/TEST AUTOMATION PROJECT - CURA Healthcare Services/Documentation/Cura Healthcare Service - Test Scenarios - 01.xlsx
+++ b/TEST AUTOMATION PROJECT - CURA Healthcare Services/Documentation/Cura Healthcare Service - Test Scenarios - 01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mabai\Desktop\Testing 2.0\TEST AUTOMATION PROJECT - CURA Healthcare Services\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mabai\Desktop\Testing 3.0\MANUAL TESTING PROJECTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40185863-2D6D-490A-A55B-5DB61A21BF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABFFF90-4E69-483C-AC8D-36DF3B87EB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{38E3547D-513B-432E-9109-DF06D717D2E9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38E3547D-513B-432E-9109-DF06D717D2E9}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="81">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -210,10 +210,6 @@
     <t>History functionality - with PRIOR APPOINTMENTS booked.</t>
   </si>
   <si>
-    <t xml:space="preserve">1-Click on the 'menu' icon.
-2-Click on the 'History' link.     </t>
-  </si>
-  <si>
     <t>TS_04</t>
   </si>
   <si>
@@ -224,9 +220,6 @@
   </si>
   <si>
     <t>TC_08</t>
-  </si>
-  <si>
-    <t>Profile functionality</t>
   </si>
   <si>
     <t>1-Click on the 'menu' icon.
@@ -236,12 +229,6 @@
     <t>Redirect to the 'History' page
 Page should display - 'No appointments'
 Page should display - 'Go to Homepage' button.</t>
-  </si>
-  <si>
-    <t>Redirection to the 'Profile' page.
-Display user details 
-Display 'Edit Details' button.
-Display 'Logout' button.</t>
   </si>
   <si>
     <t>TS_05</t>
@@ -298,6 +285,56 @@
 Addition of Test Case:
 TC_06 - TC_09
 </t>
+  </si>
+  <si>
+    <t>Username - Ashton Mayor                                                     Password - Password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-Click on the 'menu' icon.
+2-Book an appointment.
+2-Click on the 'History' link.     </t>
+  </si>
+  <si>
+    <t>Profile functionality - correct display</t>
+  </si>
+  <si>
+    <t>Edit details</t>
+  </si>
+  <si>
+    <t>Launch website - https://katalon-demo-cura.herokuapp.com/                       Successful login.  
+Successful navigation to the profile page</t>
+  </si>
+  <si>
+    <t>1-Click on the 'menu' icon.
+2-Click on the 'Profile' link.
+3-Click on the 'Edit Details' button.
+4-Edit any details
+5-Save edits
+6-Logout
+7-Login again
+8-Navigate to the profile page again</t>
+  </si>
+  <si>
+    <t>Profile page display with new details.</t>
+  </si>
+  <si>
+    <t>Redirection to the 'Profile' page.
+Display user details 
+Display 'Logout' button.</t>
+  </si>
+  <si>
+    <t>TC_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addition of Test Case:
+TC_10
+</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
@@ -705,7 +742,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E67B06-202B-4FFC-B53C-2BEBBB38C6DB}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="6"/>
@@ -715,18 +752,18 @@
   <sheetData>
     <row r="1" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -734,10 +771,10 @@
         <v>45851</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -745,10 +782,21 @@
         <v>45859</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>71</v>
+    </row>
+    <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>45943</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -822,29 +870,38 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>55</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -854,7 +911,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D67971-CD7C-47F2-A95C-93B9FB28C2C6}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="17.77734375" style="1" customWidth="1"/>
@@ -918,6 +975,9 @@
       <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -936,10 +996,13 @@
         <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="135" customHeight="1" x14ac:dyDescent="0.3">
@@ -964,6 +1027,9 @@
       <c r="G4" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -987,6 +1053,9 @@
       <c r="G5" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="I5" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1010,6 +1079,9 @@
       <c r="G6" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="I6" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="119.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1031,7 +1103,10 @@
         <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="139.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1048,7 +1123,7 @@
         <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>17</v>
@@ -1056,51 +1131,83 @@
       <c r="G8" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="I8" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>56</v>
+        <v>76</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="122.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="198" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
